--- a/healthcare_assessment_forms/022_ocean_alkalinity_assessment_form--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/022_ocean_alkalinity_assessment_form--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,9 +440,9 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>sampling_date</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date of Sampling</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>alkalinity</t>
+          <t>ocean_alkalinity_level</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alkalinity</t>
+          <t>Ocean Alkalinity Level</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>drag_and_drop_1</t>
+          <t>has_other_locations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sampling Location</t>
+          <t>Other Locations</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>drag_and_drop_2</t>
+          <t>is_temperature_range</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Water Temperature</t>
+          <t>Was Water Temperature within Range?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>drag_and_drop_3</t>
+          <t>is_salinity_range</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salinity</t>
+          <t>Was Salinity within Range?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>drag_and_drop_4</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alkalinity</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -730,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,187 +758,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>alkalinity_choices</t>
+          <t>ocean_alkalinity_level_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alkalinity_choices</t>
+          <t>ocean_alkalinity_level_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>alkalinity_choices</t>
+          <t>ocean_alkalinity_level_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>drag_and_drop_1_choices</t>
+          <t>ocean_alkalinity_level_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>drag_and_drop_1_choices</t>
+          <t>ocean_alkalinity_level_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>drag_and_drop_2_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>drag_and_drop_2_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>drag_and_drop_3_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>drag_and_drop_3_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>drag_and_drop_4_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>drag_and_drop_4_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
